--- a/exercise/Admin/Admin Keuangan/Tes Excel Admin Keuangan 1.xlsx
+++ b/exercise/Admin/Admin Keuangan/Tes Excel Admin Keuangan 1.xlsx
@@ -1,21 +1,20 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="25928"/>
-  <workbookPr defaultThemeVersion="166925"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
+  <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/a2b8a61f0eb55df9/Dokumen/Konten/Youtube/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Pemrograman\Excel\excel\exercise\Admin\Admin Keuangan\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="30" documentId="13_ncr:1_{1F90A714-6438-4500-91FD-44F693870846}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{F9B24C0F-DC39-4CD4-9217-B5FFCB061F09}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{D87DF820-F6BC-44EE-9729-1088ACA7AFEE}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160"/>
   </bookViews>
   <sheets>
     <sheet name="Soal" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="152511"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -96,7 +95,7 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <numFmts count="3">
     <numFmt numFmtId="42" formatCode="_-&quot;Rp&quot;* #,##0_-;\-&quot;Rp&quot;* #,##0_-;_-&quot;Rp&quot;* &quot;-&quot;_-;_-@_-"/>
     <numFmt numFmtId="41" formatCode="_-* #,##0_-;\-* #,##0_-;_-* &quot;-&quot;_-;_-@_-"/>
@@ -567,7 +566,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3B91A0A0-13AD-42C2-81AB-829C16959F28}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr>
     <tabColor theme="0"/>
   </sheetPr>
@@ -641,13 +640,25 @@
       <c r="D3" s="8" t="s">
         <v>6</v>
       </c>
-      <c r="E3" s="14"/>
+      <c r="E3" s="14">
+        <f>VLOOKUP(D3,$K$3:$L$13,2,FALSE)</f>
+        <v>5000000</v>
+      </c>
       <c r="F3" s="9">
         <v>2</v>
       </c>
-      <c r="G3" s="15"/>
-      <c r="H3" s="14"/>
-      <c r="I3" s="15"/>
+      <c r="G3" s="15">
+        <f>E3*F3</f>
+        <v>10000000</v>
+      </c>
+      <c r="H3" s="14">
+        <f>0.5*G3</f>
+        <v>5000000</v>
+      </c>
+      <c r="I3" s="15">
+        <f>G3+H3</f>
+        <v>15000000</v>
+      </c>
       <c r="K3" s="10" t="s">
         <v>16</v>
       </c>
@@ -665,13 +676,25 @@
       <c r="D4" s="8" t="s">
         <v>11</v>
       </c>
-      <c r="E4" s="14"/>
+      <c r="E4" s="14">
+        <f t="shared" ref="E4:E14" si="0">VLOOKUP(D4,$K$3:$L$13,2,FALSE)</f>
+        <v>30000</v>
+      </c>
       <c r="F4" s="9">
         <v>20</v>
       </c>
-      <c r="G4" s="15"/>
-      <c r="H4" s="14"/>
-      <c r="I4" s="15"/>
+      <c r="G4" s="15">
+        <f t="shared" ref="G4:G14" si="1">E4*F4</f>
+        <v>600000</v>
+      </c>
+      <c r="H4" s="14">
+        <f t="shared" ref="H4:H14" si="2">0.5*G4</f>
+        <v>300000</v>
+      </c>
+      <c r="I4" s="15">
+        <f t="shared" ref="I4:I14" si="3">G4+H4</f>
+        <v>900000</v>
+      </c>
       <c r="K4" s="8" t="s">
         <v>6</v>
       </c>
@@ -689,13 +712,25 @@
       <c r="D5" s="8" t="s">
         <v>14</v>
       </c>
-      <c r="E5" s="14"/>
+      <c r="E5" s="14">
+        <f t="shared" si="0"/>
+        <v>1500000</v>
+      </c>
       <c r="F5" s="9">
         <v>3</v>
       </c>
-      <c r="G5" s="15"/>
-      <c r="H5" s="14"/>
-      <c r="I5" s="15"/>
+      <c r="G5" s="15">
+        <f t="shared" si="1"/>
+        <v>4500000</v>
+      </c>
+      <c r="H5" s="14">
+        <f t="shared" si="2"/>
+        <v>2250000</v>
+      </c>
+      <c r="I5" s="15">
+        <f t="shared" si="3"/>
+        <v>6750000</v>
+      </c>
       <c r="K5" s="8" t="s">
         <v>7</v>
       </c>
@@ -713,13 +748,25 @@
       <c r="D6" s="8" t="s">
         <v>15</v>
       </c>
-      <c r="E6" s="14"/>
+      <c r="E6" s="14">
+        <f t="shared" si="0"/>
+        <v>300000</v>
+      </c>
       <c r="F6" s="9">
         <v>5</v>
       </c>
-      <c r="G6" s="15"/>
-      <c r="H6" s="14"/>
-      <c r="I6" s="15"/>
+      <c r="G6" s="15">
+        <f t="shared" si="1"/>
+        <v>1500000</v>
+      </c>
+      <c r="H6" s="14">
+        <f t="shared" si="2"/>
+        <v>750000</v>
+      </c>
+      <c r="I6" s="15">
+        <f t="shared" si="3"/>
+        <v>2250000</v>
+      </c>
       <c r="K6" s="8" t="s">
         <v>8</v>
       </c>
@@ -737,13 +784,25 @@
       <c r="D7" s="8" t="s">
         <v>13</v>
       </c>
-      <c r="E7" s="14"/>
+      <c r="E7" s="14">
+        <f t="shared" si="0"/>
+        <v>150000</v>
+      </c>
       <c r="F7" s="9">
         <v>10</v>
       </c>
-      <c r="G7" s="15"/>
-      <c r="H7" s="14"/>
-      <c r="I7" s="15"/>
+      <c r="G7" s="15">
+        <f t="shared" si="1"/>
+        <v>1500000</v>
+      </c>
+      <c r="H7" s="14">
+        <f t="shared" si="2"/>
+        <v>750000</v>
+      </c>
+      <c r="I7" s="15">
+        <f t="shared" si="3"/>
+        <v>2250000</v>
+      </c>
       <c r="K7" s="8" t="s">
         <v>9</v>
       </c>
@@ -761,13 +820,25 @@
       <c r="D8" s="8" t="s">
         <v>11</v>
       </c>
-      <c r="E8" s="14"/>
+      <c r="E8" s="14">
+        <f t="shared" si="0"/>
+        <v>30000</v>
+      </c>
       <c r="F8" s="9">
         <v>33</v>
       </c>
-      <c r="G8" s="15"/>
-      <c r="H8" s="14"/>
-      <c r="I8" s="15"/>
+      <c r="G8" s="15">
+        <f t="shared" si="1"/>
+        <v>990000</v>
+      </c>
+      <c r="H8" s="14">
+        <f t="shared" si="2"/>
+        <v>495000</v>
+      </c>
+      <c r="I8" s="15">
+        <f t="shared" si="3"/>
+        <v>1485000</v>
+      </c>
       <c r="K8" s="8" t="s">
         <v>10</v>
       </c>
@@ -785,13 +856,25 @@
       <c r="D9" s="8" t="s">
         <v>6</v>
       </c>
-      <c r="E9" s="14"/>
+      <c r="E9" s="14">
+        <f t="shared" si="0"/>
+        <v>5000000</v>
+      </c>
       <c r="F9" s="9">
         <v>1</v>
       </c>
-      <c r="G9" s="15"/>
-      <c r="H9" s="14"/>
-      <c r="I9" s="15"/>
+      <c r="G9" s="15">
+        <f t="shared" si="1"/>
+        <v>5000000</v>
+      </c>
+      <c r="H9" s="14">
+        <f t="shared" si="2"/>
+        <v>2500000</v>
+      </c>
+      <c r="I9" s="15">
+        <f t="shared" si="3"/>
+        <v>7500000</v>
+      </c>
       <c r="K9" s="8" t="s">
         <v>11</v>
       </c>
@@ -809,13 +892,25 @@
       <c r="D10" s="8" t="s">
         <v>11</v>
       </c>
-      <c r="E10" s="14"/>
+      <c r="E10" s="14">
+        <f t="shared" si="0"/>
+        <v>30000</v>
+      </c>
       <c r="F10" s="9">
         <v>2</v>
       </c>
-      <c r="G10" s="15"/>
-      <c r="H10" s="14"/>
-      <c r="I10" s="15"/>
+      <c r="G10" s="15">
+        <f t="shared" si="1"/>
+        <v>60000</v>
+      </c>
+      <c r="H10" s="14">
+        <f t="shared" si="2"/>
+        <v>30000</v>
+      </c>
+      <c r="I10" s="15">
+        <f t="shared" si="3"/>
+        <v>90000</v>
+      </c>
       <c r="K10" s="8" t="s">
         <v>12</v>
       </c>
@@ -833,13 +928,25 @@
       <c r="D11" s="8" t="s">
         <v>14</v>
       </c>
-      <c r="E11" s="14"/>
+      <c r="E11" s="14">
+        <f t="shared" si="0"/>
+        <v>1500000</v>
+      </c>
       <c r="F11" s="9">
         <v>3</v>
       </c>
-      <c r="G11" s="15"/>
-      <c r="H11" s="14"/>
-      <c r="I11" s="15"/>
+      <c r="G11" s="15">
+        <f t="shared" si="1"/>
+        <v>4500000</v>
+      </c>
+      <c r="H11" s="14">
+        <f t="shared" si="2"/>
+        <v>2250000</v>
+      </c>
+      <c r="I11" s="15">
+        <f t="shared" si="3"/>
+        <v>6750000</v>
+      </c>
       <c r="K11" s="8" t="s">
         <v>13</v>
       </c>
@@ -857,13 +964,25 @@
       <c r="D12" s="8" t="s">
         <v>15</v>
       </c>
-      <c r="E12" s="14"/>
+      <c r="E12" s="14">
+        <f t="shared" si="0"/>
+        <v>300000</v>
+      </c>
       <c r="F12" s="9">
         <v>4</v>
       </c>
-      <c r="G12" s="15"/>
-      <c r="H12" s="14"/>
-      <c r="I12" s="15"/>
+      <c r="G12" s="15">
+        <f t="shared" si="1"/>
+        <v>1200000</v>
+      </c>
+      <c r="H12" s="14">
+        <f t="shared" si="2"/>
+        <v>600000</v>
+      </c>
+      <c r="I12" s="15">
+        <f t="shared" si="3"/>
+        <v>1800000</v>
+      </c>
       <c r="K12" s="8" t="s">
         <v>14</v>
       </c>
@@ -881,13 +1000,25 @@
       <c r="D13" s="8" t="s">
         <v>13</v>
       </c>
-      <c r="E13" s="14"/>
+      <c r="E13" s="14">
+        <f t="shared" si="0"/>
+        <v>150000</v>
+      </c>
       <c r="F13" s="9">
         <v>5</v>
       </c>
-      <c r="G13" s="15"/>
-      <c r="H13" s="14"/>
-      <c r="I13" s="15"/>
+      <c r="G13" s="15">
+        <f t="shared" si="1"/>
+        <v>750000</v>
+      </c>
+      <c r="H13" s="14">
+        <f t="shared" si="2"/>
+        <v>375000</v>
+      </c>
+      <c r="I13" s="15">
+        <f t="shared" si="3"/>
+        <v>1125000</v>
+      </c>
       <c r="K13" s="8" t="s">
         <v>15</v>
       </c>
@@ -905,13 +1036,25 @@
       <c r="D14" s="8" t="s">
         <v>11</v>
       </c>
-      <c r="E14" s="14"/>
+      <c r="E14" s="14">
+        <f t="shared" si="0"/>
+        <v>30000</v>
+      </c>
       <c r="F14" s="9">
         <v>6</v>
       </c>
-      <c r="G14" s="15"/>
-      <c r="H14" s="14"/>
-      <c r="I14" s="15"/>
+      <c r="G14" s="15">
+        <f t="shared" si="1"/>
+        <v>180000</v>
+      </c>
+      <c r="H14" s="14">
+        <f t="shared" si="2"/>
+        <v>90000</v>
+      </c>
+      <c r="I14" s="15">
+        <f t="shared" si="3"/>
+        <v>270000</v>
+      </c>
     </row>
   </sheetData>
   <mergeCells count="2">

--- a/exercise/Admin/Admin Keuangan/Tes Excel Admin Keuangan 1.xlsx
+++ b/exercise/Admin/Admin Keuangan/Tes Excel Admin Keuangan 1.xlsx
@@ -1,23 +1,33 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
-  <workbookPr/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28925"/>
+  <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Pemrograman\Excel\excel\exercise\Admin\Admin Keuangan\"/>
     </mc:Choice>
   </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A9BC7B99-D96B-418D-A60D-70F1B2F664D9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11310" xr2:uid="{D87DF820-F6BC-44EE-9729-1088ACA7AFEE}"/>
   </bookViews>
   <sheets>
     <sheet name="Soal" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="152511"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
+    </ext>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+      </xcalcf:calcFeatures>
     </ext>
   </extLst>
 </workbook>
@@ -95,7 +105,7 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="3">
     <numFmt numFmtId="42" formatCode="_-&quot;Rp&quot;* #,##0_-;\-&quot;Rp&quot;* #,##0_-;_-&quot;Rp&quot;* &quot;-&quot;_-;_-@_-"/>
     <numFmt numFmtId="41" formatCode="_-* #,##0_-;\-* #,##0_-;_-* &quot;-&quot;_-;_-@_-"/>
@@ -559,14 +569,14 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme 2013 - 2022" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3B91A0A0-13AD-42C2-81AB-829C16959F28}">
   <sheetPr>
     <tabColor theme="0"/>
   </sheetPr>
@@ -652,12 +662,12 @@
         <v>10000000</v>
       </c>
       <c r="H3" s="14">
-        <f>0.5*G3</f>
-        <v>5000000</v>
+        <f>5%*G3</f>
+        <v>500000</v>
       </c>
       <c r="I3" s="15">
         <f>G3+H3</f>
-        <v>15000000</v>
+        <v>10500000</v>
       </c>
       <c r="K3" s="10" t="s">
         <v>16</v>
@@ -688,12 +698,12 @@
         <v>600000</v>
       </c>
       <c r="H4" s="14">
-        <f t="shared" ref="H4:H14" si="2">0.5*G4</f>
-        <v>300000</v>
+        <f t="shared" ref="H4:H14" si="2">5%*G4</f>
+        <v>30000</v>
       </c>
       <c r="I4" s="15">
         <f t="shared" ref="I4:I14" si="3">G4+H4</f>
-        <v>900000</v>
+        <v>630000</v>
       </c>
       <c r="K4" s="8" t="s">
         <v>6</v>
@@ -725,11 +735,11 @@
       </c>
       <c r="H5" s="14">
         <f t="shared" si="2"/>
-        <v>2250000</v>
+        <v>225000</v>
       </c>
       <c r="I5" s="15">
         <f t="shared" si="3"/>
-        <v>6750000</v>
+        <v>4725000</v>
       </c>
       <c r="K5" s="8" t="s">
         <v>7</v>
@@ -761,11 +771,11 @@
       </c>
       <c r="H6" s="14">
         <f t="shared" si="2"/>
-        <v>750000</v>
+        <v>75000</v>
       </c>
       <c r="I6" s="15">
         <f t="shared" si="3"/>
-        <v>2250000</v>
+        <v>1575000</v>
       </c>
       <c r="K6" s="8" t="s">
         <v>8</v>
@@ -797,11 +807,11 @@
       </c>
       <c r="H7" s="14">
         <f t="shared" si="2"/>
-        <v>750000</v>
+        <v>75000</v>
       </c>
       <c r="I7" s="15">
         <f t="shared" si="3"/>
-        <v>2250000</v>
+        <v>1575000</v>
       </c>
       <c r="K7" s="8" t="s">
         <v>9</v>
@@ -833,11 +843,11 @@
       </c>
       <c r="H8" s="14">
         <f t="shared" si="2"/>
-        <v>495000</v>
+        <v>49500</v>
       </c>
       <c r="I8" s="15">
         <f t="shared" si="3"/>
-        <v>1485000</v>
+        <v>1039500</v>
       </c>
       <c r="K8" s="8" t="s">
         <v>10</v>
@@ -869,11 +879,11 @@
       </c>
       <c r="H9" s="14">
         <f t="shared" si="2"/>
-        <v>2500000</v>
+        <v>250000</v>
       </c>
       <c r="I9" s="15">
         <f t="shared" si="3"/>
-        <v>7500000</v>
+        <v>5250000</v>
       </c>
       <c r="K9" s="8" t="s">
         <v>11</v>
@@ -905,11 +915,11 @@
       </c>
       <c r="H10" s="14">
         <f t="shared" si="2"/>
-        <v>30000</v>
+        <v>3000</v>
       </c>
       <c r="I10" s="15">
         <f t="shared" si="3"/>
-        <v>90000</v>
+        <v>63000</v>
       </c>
       <c r="K10" s="8" t="s">
         <v>12</v>
@@ -941,11 +951,11 @@
       </c>
       <c r="H11" s="14">
         <f t="shared" si="2"/>
-        <v>2250000</v>
+        <v>225000</v>
       </c>
       <c r="I11" s="15">
         <f t="shared" si="3"/>
-        <v>6750000</v>
+        <v>4725000</v>
       </c>
       <c r="K11" s="8" t="s">
         <v>13</v>
@@ -977,11 +987,11 @@
       </c>
       <c r="H12" s="14">
         <f t="shared" si="2"/>
-        <v>600000</v>
+        <v>60000</v>
       </c>
       <c r="I12" s="15">
         <f t="shared" si="3"/>
-        <v>1800000</v>
+        <v>1260000</v>
       </c>
       <c r="K12" s="8" t="s">
         <v>14</v>
@@ -1013,11 +1023,11 @@
       </c>
       <c r="H13" s="14">
         <f t="shared" si="2"/>
-        <v>375000</v>
+        <v>37500</v>
       </c>
       <c r="I13" s="15">
         <f t="shared" si="3"/>
-        <v>1125000</v>
+        <v>787500</v>
       </c>
       <c r="K13" s="8" t="s">
         <v>15</v>
@@ -1049,11 +1059,11 @@
       </c>
       <c r="H14" s="14">
         <f t="shared" si="2"/>
-        <v>90000</v>
+        <v>9000</v>
       </c>
       <c r="I14" s="15">
         <f t="shared" si="3"/>
-        <v>270000</v>
+        <v>189000</v>
       </c>
     </row>
   </sheetData>
